--- a/fhir/core/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/fhir/core/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.5.0</t>
+    <t>3.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T17:27:08+01:00</t>
+    <t>2026-03-11T23:16:27+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>GRNDCHILD</t>
+  </si>
+  <si>
+    <t>GRPRN</t>
   </si>
   <si>
     <t>CHLDINLAW</t>
@@ -436,7 +439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -569,16 +572,22 @@
       <c r="A21" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="B21" t="s" s="2">
-        <v>47</v>
-      </c>
+      <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
         <v>48</v>
       </c>
       <c r="B22" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>49</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -597,28 +606,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/core/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/fhir/core/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.6.0</t>
+    <t>3.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T23:16:27+01:00</t>
+    <t>2026-05-30T15:25:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
